--- a/vorlage/Wareneingang-Vorlage.xlsx
+++ b/vorlage/Wareneingang-Vorlage.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +52,18 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -149,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -163,7 +173,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -174,6 +184,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -193,6 +206,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -690,8 +706,15 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Positionen im Dokument</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Kunde / Client</t>
         </is>
@@ -700,11 +723,15 @@
         <f>IFERROR(INDEX(Daten!$B$2:$B$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="J10" s="2">
+        <f>COUNTIF(Daten!$A$2:$A$20001,$J$2)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Lieferant / Supplier</t>
         </is>
@@ -713,8 +740,8 @@
         <f>IFERROR(INDEX(Daten!$C$2:$C$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -725,61 +752,61 @@
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Artikelbezeichnung / Article description</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Anzahl / QTY</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>MHD / Expiration Date</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Regalplatznr., eralten durch Secend Team/shelf no. received by Secend Team</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>Bemerkungen /Kontrolle
 Comments / Checks</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>Bestehend / Existing</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="14">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="15">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="15">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -791,28 +818,28 @@
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="14">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="16">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="14">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="15">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="15">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -824,28 +851,28 @@
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="14">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="16">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="14">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="15">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="15">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -857,28 +884,28 @@
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="14">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="16">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="12" t="n">
+      <c r="A19" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="14">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="15">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="15">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -890,28 +917,28 @@
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="14">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="16">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="12" t="n">
+      <c r="A20" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="14">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="15">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="15">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -923,28 +950,28 @@
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="14">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="16">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="12" t="n">
+      <c r="A21" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="14">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="15">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="15">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -956,28 +983,28 @@
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="14">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="16">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="14">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="15">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="15">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -989,28 +1016,28 @@
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="14">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="16">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="14">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="15">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="15">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -1022,28 +1049,28 @@
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="14">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="16">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="14">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="15">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="15">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -1055,28 +1082,28 @@
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="14">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="16">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="14">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="15">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="15">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -1088,41 +1115,47 @@
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="14">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="16">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="17">
+        <f>IF($J$2="","",IF($J$10=0,"Zu dieser Nummer stehen keine Zeilen im Blatt Daten — aktualisieren, oder der Suchbereich reicht nicht.",IF($J$10&gt;10,"Achtung: dieser Wareneingang hat "&amp;$J$10&amp;" Positionen. Hier stehen nur die ersten 10.","")))</f>
+        <v/>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Lagerfläche / storage space</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
+      <c r="B27" s="11" t="n"/>
       <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Umrechung/Conversion</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>m2 Anzahl / m2 quantity</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="14">
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="15">
         <f>IFERROR(INDEX(Daten!$D$2:$D$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>1 g = 0.001 kg</t>
         </is>
@@ -1134,15 +1167,16 @@
           <t>Bemerkung</t>
         </is>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="18">
         <f>IFERROR(INDEX(Daten!$E$2:$E$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="J4:J7"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="B30:H30"/>
@@ -1195,117 +1229,117 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>WeNr</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Kunde</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Lieferant</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>LagerM2</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>KopfBemerkung</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="19" t="inlineStr">
         <is>
           <t>AngNam</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="G1" s="19" t="inlineStr">
         <is>
           <t>AngDat</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="H1" s="19" t="inlineStr">
         <is>
           <t>AngZeit</t>
         </is>
       </c>
-      <c r="I1" s="17" t="inlineStr">
+      <c r="I1" s="19" t="inlineStr">
         <is>
           <t>GezNam</t>
         </is>
       </c>
-      <c r="J1" s="17" t="inlineStr">
+      <c r="J1" s="19" t="inlineStr">
         <is>
           <t>GezDat</t>
         </is>
       </c>
-      <c r="K1" s="17" t="inlineStr">
+      <c r="K1" s="19" t="inlineStr">
         <is>
           <t>GezZeit</t>
         </is>
       </c>
-      <c r="L1" s="17" t="inlineStr">
+      <c r="L1" s="19" t="inlineStr">
         <is>
           <t>EinNam</t>
         </is>
       </c>
-      <c r="M1" s="17" t="inlineStr">
+      <c r="M1" s="19" t="inlineStr">
         <is>
           <t>EinDat</t>
         </is>
       </c>
-      <c r="N1" s="17" t="inlineStr">
+      <c r="N1" s="19" t="inlineStr">
         <is>
           <t>EinZeit</t>
         </is>
       </c>
-      <c r="O1" s="17" t="inlineStr">
+      <c r="O1" s="19" t="inlineStr">
         <is>
           <t>Nr</t>
         </is>
       </c>
-      <c r="P1" s="17" t="inlineStr">
+      <c r="P1" s="19" t="inlineStr">
         <is>
           <t>Artikel</t>
         </is>
       </c>
-      <c r="Q1" s="17" t="inlineStr">
+      <c r="Q1" s="19" t="inlineStr">
         <is>
           <t>Anzahl</t>
         </is>
       </c>
-      <c r="R1" s="17" t="inlineStr">
+      <c r="R1" s="19" t="inlineStr">
         <is>
           <t>KG</t>
         </is>
       </c>
-      <c r="S1" s="17" t="inlineStr">
+      <c r="S1" s="19" t="inlineStr">
         <is>
           <t>MHD</t>
         </is>
       </c>
-      <c r="T1" s="17" t="inlineStr">
+      <c r="T1" s="19" t="inlineStr">
         <is>
           <t>Regalplatz</t>
         </is>
       </c>
-      <c r="U1" s="17" t="inlineStr">
+      <c r="U1" s="19" t="inlineStr">
         <is>
           <t>Bemerkung</t>
         </is>
       </c>
-      <c r="V1" s="17" t="inlineStr">
+      <c r="V1" s="19" t="inlineStr">
         <is>
           <t>Bestehend</t>
         </is>
       </c>
-      <c r="W1" s="17" t="inlineStr">
+      <c r="W1" s="19" t="inlineStr">
         <is>
           <t>Schluessel</t>
         </is>
@@ -1329,7 +1363,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>WeNr</t>
         </is>
@@ -1375,117 +1409,117 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>WeNr</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Kunde</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Lieferant</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>LagerM2</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>KopfBemerkung</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="19" t="inlineStr">
         <is>
           <t>AngNam</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="G1" s="19" t="inlineStr">
         <is>
           <t>AngDat</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="H1" s="19" t="inlineStr">
         <is>
           <t>AngZeit</t>
         </is>
       </c>
-      <c r="I1" s="17" t="inlineStr">
+      <c r="I1" s="19" t="inlineStr">
         <is>
           <t>GezNam</t>
         </is>
       </c>
-      <c r="J1" s="17" t="inlineStr">
+      <c r="J1" s="19" t="inlineStr">
         <is>
           <t>GezDat</t>
         </is>
       </c>
-      <c r="K1" s="17" t="inlineStr">
+      <c r="K1" s="19" t="inlineStr">
         <is>
           <t>GezZeit</t>
         </is>
       </c>
-      <c r="L1" s="17" t="inlineStr">
+      <c r="L1" s="19" t="inlineStr">
         <is>
           <t>EinNam</t>
         </is>
       </c>
-      <c r="M1" s="17" t="inlineStr">
+      <c r="M1" s="19" t="inlineStr">
         <is>
           <t>EinDat</t>
         </is>
       </c>
-      <c r="N1" s="17" t="inlineStr">
+      <c r="N1" s="19" t="inlineStr">
         <is>
           <t>EinZeit</t>
         </is>
       </c>
-      <c r="O1" s="17" t="inlineStr">
+      <c r="O1" s="19" t="inlineStr">
         <is>
           <t>Nr</t>
         </is>
       </c>
-      <c r="P1" s="17" t="inlineStr">
+      <c r="P1" s="19" t="inlineStr">
         <is>
           <t>Artikel</t>
         </is>
       </c>
-      <c r="Q1" s="17" t="inlineStr">
+      <c r="Q1" s="19" t="inlineStr">
         <is>
           <t>Anzahl</t>
         </is>
       </c>
-      <c r="R1" s="17" t="inlineStr">
+      <c r="R1" s="19" t="inlineStr">
         <is>
           <t>KG</t>
         </is>
       </c>
-      <c r="S1" s="17" t="inlineStr">
+      <c r="S1" s="19" t="inlineStr">
         <is>
           <t>MHD</t>
         </is>
       </c>
-      <c r="T1" s="17" t="inlineStr">
+      <c r="T1" s="19" t="inlineStr">
         <is>
           <t>Regalplatz</t>
         </is>
       </c>
-      <c r="U1" s="17" t="inlineStr">
+      <c r="U1" s="19" t="inlineStr">
         <is>
           <t>Bemerkung</t>
         </is>
       </c>
-      <c r="V1" s="17" t="inlineStr">
+      <c r="V1" s="19" t="inlineStr">
         <is>
           <t>Bestehend</t>
         </is>
       </c>
-      <c r="W1" s="17" t="inlineStr">
+      <c r="W1" s="19" t="inlineStr">
         <is>
           <t>Schluessel</t>
         </is>

--- a/vorlage/Wareneingang-Vorlage.xlsx
+++ b/vorlage/Wareneingang-Vorlage.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,11 +53,6 @@
     <font>
       <name val="Arial"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -133,7 +128,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
       <top style="thin">
         <color rgb="00000000"/>
       </top>
@@ -144,9 +141,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="00000000"/>
       </top>
@@ -173,7 +168,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -191,7 +187,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
@@ -207,7 +202,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -611,95 +606,101 @@
     <row r="2">
       <c r="J2" s="3" t="inlineStr"/>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Aufgabe / Task</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Name Mitarbeiter / Employee name</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Datum / Date</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Uhrzeit / Time</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Angenommen /
-Accepted</t>
-        </is>
-      </c>
-      <c r="B4" s="6">
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Angenommen / Accepted</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="7">
         <f>IFERROR(INDEX(Daten!$F$2:$F$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C4" s="6">
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="7">
         <f>IFERROR(INDEX(Daten!$G$2:$G$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D4" s="6">
+      <c r="F4" s="7">
         <f>IFERROR(INDEX(Daten!$H$2:$H$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Nur diese Zelle wird von Hand geändert. Alles andere füllt sich selbst.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Gezählt &amp; kontrolliert /
-counted &amp; controlled</t>
-        </is>
-      </c>
-      <c r="B5" s="6">
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Gezählt &amp; kontrolliert / counted &amp; controlled</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="7">
         <f>IFERROR(INDEX(Daten!$I$2:$I$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C5" s="6">
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="7">
         <f>IFERROR(INDEX(Daten!$J$2:$J$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D5" s="6">
+      <c r="F5" s="7">
         <f>IFERROR(INDEX(Daten!$K$2:$K$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Eingelagert / stored</t>
         </is>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="7">
         <f>IFERROR(INDEX(Daten!$L$2:$L$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C6" s="6">
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="7">
         <f>IFERROR(INDEX(Daten!$M$2:$M$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D6" s="6">
+      <c r="F6" s="7">
         <f>IFERROR(INDEX(Daten!$N$2:$N$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="7"/>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Artikelanzahl bitte direkt auf dem Lieferschein abhaken bzw. anpassen.
 Please check off or adapt the article quantities directly on the delivery slip</t>
@@ -707,44 +708,48 @@
       </c>
     </row>
     <row r="9">
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>Positionen im Dokument</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Kunde / Client</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="7">
         <f>IFERROR(INDEX(Daten!$B$2:$B$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
       <c r="J10" s="2">
         <f>COUNTIF(Daten!$A$2:$A$20001,$J$2)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Lieferant / Supplier</t>
         </is>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="7">
         <f>IFERROR(INDEX(Daten!$C$2:$C$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Bei neuem und bestehendem Material mit oder ohne Lieferschein notwendig:
 For new and existing material with or without delivery slip needed</t>
@@ -810,11 +815,11 @@
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="7">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -843,11 +848,11 @@
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="7">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="7">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -876,11 +881,11 @@
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="7">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="7">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -909,11 +914,11 @@
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="7">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="7">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -942,11 +947,11 @@
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="7">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="7">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -975,11 +980,11 @@
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="7">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="7">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -1008,11 +1013,11 @@
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="7">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="7">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -1041,11 +1046,11 @@
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="7">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="7">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -1074,11 +1079,11 @@
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="7">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="7">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -1107,11 +1112,11 @@
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="7">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="7">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
@@ -1131,31 +1136,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Lagerfläche / storage space</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="7" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Umrechung/Conversion</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>m2 Anzahl / m2 quantity</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
+      <c r="B28" s="5" t="n"/>
       <c r="C28" s="15">
         <f>IFERROR(INDEX(Daten!$D$2:$D$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>1 g = 0.001 kg</t>
         </is>
@@ -1173,16 +1178,26 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
+  <mergeCells count="19">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="J4:J7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="B30:H30"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C3:D3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="J2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Diese Nummer steht nicht in der Liste." prompt="Wareneingang aus der Liste wählen" type="list">

--- a/vorlage/Wareneingang-Vorlage.xlsx
+++ b/vorlage/Wareneingang-Vorlage.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -154,61 +159,64 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -597,110 +605,114 @@
           <t>Wareneingang / Material reception</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="F1" s="2">
+        <f>IF($J$2="","",$J$2)</f>
+        <v/>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Wareneingang wählen</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="J2" s="3" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr"/>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Aufgabe / Task</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Name Mitarbeiter / Employee name</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Datum / Date</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Uhrzeit / Time</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Angenommen / Accepted</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="7">
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="8">
         <f>IFERROR(INDEX(Daten!$F$2:$F$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="7">
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="8">
         <f>IFERROR(INDEX(Daten!$G$2:$G$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="8">
         <f>IFERROR(INDEX(Daten!$H$2:$H$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>Nur diese Zelle wird von Hand geändert. Alles andere füllt sich selbst.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Gezählt &amp; kontrolliert / counted &amp; controlled</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="7">
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="8">
         <f>IFERROR(INDEX(Daten!$I$2:$I$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="7">
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="8">
         <f>IFERROR(INDEX(Daten!$J$2:$J$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <f>IFERROR(INDEX(Daten!$K$2:$K$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Eingelagert / stored</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="7">
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="8">
         <f>IFERROR(INDEX(Daten!$L$2:$L$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="7">
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="8">
         <f>IFERROR(INDEX(Daten!$M$2:$M$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>IFERROR(INDEX(Daten!$N$2:$N$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="7"/>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Artikelanzahl bitte direkt auf dem Lieferschein abhaken bzw. anpassen.
 Please check off or adapt the article quantities directly on the delivery slip</t>
@@ -708,48 +720,48 @@
       </c>
     </row>
     <row r="9">
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>Positionen im Dokument</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Kunde / Client</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="7">
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="8">
         <f>IFERROR(INDEX(Daten!$B$2:$B$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="J10" s="2">
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="J10" s="3">
         <f>COUNTIF(Daten!$A$2:$A$20001,$J$2)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Lieferant / Supplier</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="7">
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="8">
         <f>IFERROR(INDEX(Daten!$C$2:$C$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Bei neuem und bestehendem Material mit oder ohne Lieferschein notwendig:
 For new and existing material with or without delivery slip needed</t>
@@ -757,428 +769,428 @@
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Artikelbezeichnung / Article description</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Anzahl / QTY</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>MHD / Expiration Date</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Regalplatznr., eralten durch Secend Team/shelf no. received by Secend Team</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>Bemerkungen /Kontrolle
 Comments / Checks</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>Bestehend / Existing</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="13" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="15">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="16">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="16">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="15">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="17">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A16,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="13" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="15">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="16">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="16">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="15">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="17">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A17,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="13" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="15">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="16">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="16">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="8">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="15">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="17">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A18,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="13" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="15">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="16">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="16">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="15">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="17">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A19,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="13" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="15">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="16">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="16">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="8">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="15">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="17">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A20,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="13" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="15">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="16">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="16">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="8">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="15">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="17">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A21,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="13" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="15">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="16">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="16">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="8">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="8">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="15">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="17">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A22,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="13" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="15">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="16">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="16">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="8">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="8">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="15">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="17">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A23,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="13" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="15">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="16">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="16">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="8">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="8">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="15">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="17">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A24,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="13" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="15">
         <f>IFERROR(INDEX(Daten!$P$2:$P$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="16">
         <f>IFERROR(INDEX(Daten!$Q$2:$Q$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="16">
         <f>IFERROR(INDEX(Daten!$R$2:$R$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="8">
         <f>IFERROR(INDEX(Daten!$S$2:$S$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="8">
         <f>IFERROR(INDEX(Daten!$T$2:$T$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="15">
         <f>IFERROR(INDEX(Daten!$U$2:$U$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="17">
         <f>IFERROR(INDEX(Daten!$V$2:$V$20001,MATCH($J$2&amp;"-"&amp;$A25,Daten!$W$2:$W$20001,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17">
+      <c r="A26" s="18">
         <f>IF($J$2="","",IF($J$10=0,"Zu dieser Nummer stehen keine Zeilen im Blatt Daten — aktualisieren, oder der Suchbereich reicht nicht.",IF($J$10&gt;10,"Achtung: dieser Wareneingang hat "&amp;$J$10&amp;" Positionen. Hier stehen nur die ersten 10.","")))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Lagerfläche / storage space</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="8" t="inlineStr"/>
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Umrechung/Conversion</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>m2 Anzahl / m2 quantity</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="15">
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="16">
         <f>IFERROR(INDEX(Daten!$D$2:$D$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>1 g = 0.001 kg</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Bemerkung</t>
         </is>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="19">
         <f>IFERROR(INDEX(Daten!$E$2:$E$20001,MATCH($J$2,Daten!$A$2:$A$20001,0)),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
@@ -1189,6 +1201,7 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="J4:J7"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="A8:H8"/>
@@ -1244,117 +1257,117 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>WeNr</t>
         </is>
       </c>
-      <c r="B1" s="19" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Kunde</t>
         </is>
       </c>
-      <c r="C1" s="19" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Lieferant</t>
         </is>
       </c>
-      <c r="D1" s="19" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>LagerM2</t>
         </is>
       </c>
-      <c r="E1" s="19" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>KopfBemerkung</t>
         </is>
       </c>
-      <c r="F1" s="19" t="inlineStr">
+      <c r="F1" s="20" t="inlineStr">
         <is>
           <t>AngNam</t>
         </is>
       </c>
-      <c r="G1" s="19" t="inlineStr">
+      <c r="G1" s="20" t="inlineStr">
         <is>
           <t>AngDat</t>
         </is>
       </c>
-      <c r="H1" s="19" t="inlineStr">
+      <c r="H1" s="20" t="inlineStr">
         <is>
           <t>AngZeit</t>
         </is>
       </c>
-      <c r="I1" s="19" t="inlineStr">
+      <c r="I1" s="20" t="inlineStr">
         <is>
           <t>GezNam</t>
         </is>
       </c>
-      <c r="J1" s="19" t="inlineStr">
+      <c r="J1" s="20" t="inlineStr">
         <is>
           <t>GezDat</t>
         </is>
       </c>
-      <c r="K1" s="19" t="inlineStr">
+      <c r="K1" s="20" t="inlineStr">
         <is>
           <t>GezZeit</t>
         </is>
       </c>
-      <c r="L1" s="19" t="inlineStr">
+      <c r="L1" s="20" t="inlineStr">
         <is>
           <t>EinNam</t>
         </is>
       </c>
-      <c r="M1" s="19" t="inlineStr">
+      <c r="M1" s="20" t="inlineStr">
         <is>
           <t>EinDat</t>
         </is>
       </c>
-      <c r="N1" s="19" t="inlineStr">
+      <c r="N1" s="20" t="inlineStr">
         <is>
           <t>EinZeit</t>
         </is>
       </c>
-      <c r="O1" s="19" t="inlineStr">
+      <c r="O1" s="20" t="inlineStr">
         <is>
           <t>Nr</t>
         </is>
       </c>
-      <c r="P1" s="19" t="inlineStr">
+      <c r="P1" s="20" t="inlineStr">
         <is>
           <t>Artikel</t>
         </is>
       </c>
-      <c r="Q1" s="19" t="inlineStr">
+      <c r="Q1" s="20" t="inlineStr">
         <is>
           <t>Anzahl</t>
         </is>
       </c>
-      <c r="R1" s="19" t="inlineStr">
+      <c r="R1" s="20" t="inlineStr">
         <is>
           <t>KG</t>
         </is>
       </c>
-      <c r="S1" s="19" t="inlineStr">
+      <c r="S1" s="20" t="inlineStr">
         <is>
           <t>MHD</t>
         </is>
       </c>
-      <c r="T1" s="19" t="inlineStr">
+      <c r="T1" s="20" t="inlineStr">
         <is>
           <t>Regalplatz</t>
         </is>
       </c>
-      <c r="U1" s="19" t="inlineStr">
+      <c r="U1" s="20" t="inlineStr">
         <is>
           <t>Bemerkung</t>
         </is>
       </c>
-      <c r="V1" s="19" t="inlineStr">
+      <c r="V1" s="20" t="inlineStr">
         <is>
           <t>Bestehend</t>
         </is>
       </c>
-      <c r="W1" s="19" t="inlineStr">
+      <c r="W1" s="20" t="inlineStr">
         <is>
           <t>Schluessel</t>
         </is>
@@ -1378,7 +1391,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>WeNr</t>
         </is>
@@ -1424,117 +1437,117 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>WeNr</t>
         </is>
       </c>
-      <c r="B1" s="19" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Kunde</t>
         </is>
       </c>
-      <c r="C1" s="19" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Lieferant</t>
         </is>
       </c>
-      <c r="D1" s="19" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>LagerM2</t>
         </is>
       </c>
-      <c r="E1" s="19" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>KopfBemerkung</t>
         </is>
       </c>
-      <c r="F1" s="19" t="inlineStr">
+      <c r="F1" s="20" t="inlineStr">
         <is>
           <t>AngNam</t>
         </is>
       </c>
-      <c r="G1" s="19" t="inlineStr">
+      <c r="G1" s="20" t="inlineStr">
         <is>
           <t>AngDat</t>
         </is>
       </c>
-      <c r="H1" s="19" t="inlineStr">
+      <c r="H1" s="20" t="inlineStr">
         <is>
           <t>AngZeit</t>
         </is>
       </c>
-      <c r="I1" s="19" t="inlineStr">
+      <c r="I1" s="20" t="inlineStr">
         <is>
           <t>GezNam</t>
         </is>
       </c>
-      <c r="J1" s="19" t="inlineStr">
+      <c r="J1" s="20" t="inlineStr">
         <is>
           <t>GezDat</t>
         </is>
       </c>
-      <c r="K1" s="19" t="inlineStr">
+      <c r="K1" s="20" t="inlineStr">
         <is>
           <t>GezZeit</t>
         </is>
       </c>
-      <c r="L1" s="19" t="inlineStr">
+      <c r="L1" s="20" t="inlineStr">
         <is>
           <t>EinNam</t>
         </is>
       </c>
-      <c r="M1" s="19" t="inlineStr">
+      <c r="M1" s="20" t="inlineStr">
         <is>
           <t>EinDat</t>
         </is>
       </c>
-      <c r="N1" s="19" t="inlineStr">
+      <c r="N1" s="20" t="inlineStr">
         <is>
           <t>EinZeit</t>
         </is>
       </c>
-      <c r="O1" s="19" t="inlineStr">
+      <c r="O1" s="20" t="inlineStr">
         <is>
           <t>Nr</t>
         </is>
       </c>
-      <c r="P1" s="19" t="inlineStr">
+      <c r="P1" s="20" t="inlineStr">
         <is>
           <t>Artikel</t>
         </is>
       </c>
-      <c r="Q1" s="19" t="inlineStr">
+      <c r="Q1" s="20" t="inlineStr">
         <is>
           <t>Anzahl</t>
         </is>
       </c>
-      <c r="R1" s="19" t="inlineStr">
+      <c r="R1" s="20" t="inlineStr">
         <is>
           <t>KG</t>
         </is>
       </c>
-      <c r="S1" s="19" t="inlineStr">
+      <c r="S1" s="20" t="inlineStr">
         <is>
           <t>MHD</t>
         </is>
       </c>
-      <c r="T1" s="19" t="inlineStr">
+      <c r="T1" s="20" t="inlineStr">
         <is>
           <t>Regalplatz</t>
         </is>
       </c>
-      <c r="U1" s="19" t="inlineStr">
+      <c r="U1" s="20" t="inlineStr">
         <is>
           <t>Bemerkung</t>
         </is>
       </c>
-      <c r="V1" s="19" t="inlineStr">
+      <c r="V1" s="20" t="inlineStr">
         <is>
           <t>Bestehend</t>
         </is>
       </c>
-      <c r="W1" s="19" t="inlineStr">
+      <c r="W1" s="20" t="inlineStr">
         <is>
           <t>Schluessel</t>
         </is>
